--- a/StaAna_Ex3A_Tables_1.xlsx
+++ b/StaAna_Ex3A_Tables_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thaniastaana\DATA_Labs\W2_Workshop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E9DAC2A-585A-4A9D-99FD-D85F63A7EFC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{EE883929-7BA9-4A71-B5AB-D613F7388065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{6C553E69-CA2E-49C6-90EF-D3627EE73433}"/>
   </bookViews>
@@ -91,9 +91,6 @@
     <t>ServiceName</t>
   </si>
   <si>
-    <t>DurationMIn</t>
-  </si>
-  <si>
     <t>StandardPricing</t>
   </si>
   <si>
@@ -103,9 +100,6 @@
     <t>StartTime</t>
   </si>
   <si>
-    <t>AmoutCharged</t>
-  </si>
-  <si>
     <t>WalkNotes</t>
   </si>
   <si>
@@ -299,6 +293,12 @@
   </si>
   <si>
     <t>Met a dog</t>
+  </si>
+  <si>
+    <t>DurationMin</t>
+  </si>
+  <si>
+    <t>AmountCharged</t>
   </si>
 </sst>
 </file>
@@ -743,16 +743,16 @@
         <v>1001</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -760,16 +760,16 @@
         <v>1002</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -777,16 +777,16 @@
         <v>1003</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -794,16 +794,16 @@
         <v>1004</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -811,16 +811,16 @@
         <v>1005</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -828,16 +828,16 @@
         <v>1006</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -884,13 +884,13 @@
         <v>1001</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E2">
         <v>1001</v>
@@ -901,13 +901,13 @@
         <v>1002</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E3">
         <v>1002</v>
@@ -918,13 +918,13 @@
         <v>1003</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E4">
         <v>1003</v>
@@ -935,13 +935,13 @@
         <v>1004</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E5">
         <v>1004</v>
@@ -952,13 +952,13 @@
         <v>1005</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" t="s">
         <v>55</v>
-      </c>
-      <c r="D6" t="s">
-        <v>57</v>
       </c>
       <c r="E6">
         <v>1005</v>
@@ -969,13 +969,13 @@
         <v>1006</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E7">
         <v>1006</v>
@@ -1013,13 +1013,13 @@
         <v>1001</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1027,13 +1027,13 @@
         <v>1002</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1041,13 +1041,13 @@
         <v>1003</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1055,13 +1055,13 @@
         <v>1004</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1069,13 +1069,13 @@
         <v>1005</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -1083,13 +1083,13 @@
         <v>1006</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1121,10 +1121,10 @@
         <v>14</v>
       </c>
       <c r="C1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" t="s">
         <v>15</v>
-      </c>
-      <c r="D1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -1132,7 +1132,7 @@
         <v>1001</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C2">
         <v>60</v>
@@ -1156,19 +1156,19 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" t="s">
         <v>18</v>
-      </c>
-      <c r="D1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" t="s">
-        <v>20</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>9</v>
@@ -1191,7 +1191,7 @@
         <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F2">
         <v>1004</v>
@@ -1214,7 +1214,7 @@
         <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F3">
         <v>1002</v>
@@ -1237,7 +1237,7 @@
         <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F4">
         <v>1001</v>
@@ -1260,7 +1260,7 @@
         <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F5">
         <v>1005</v>
@@ -1283,7 +1283,7 @@
         <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F6">
         <v>1006</v>
@@ -1306,7 +1306,7 @@
         <v>100</v>
       </c>
       <c r="E7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F7">
         <v>1003</v>
@@ -1327,13 +1327,13 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>5</v>
